--- a/public/templates/발주서양식.xlsx
+++ b/public/templates/발주서양식.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\서재형\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\서재형\Desktop\new\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F8ACFA-6C72-4604-A60D-056609406567}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6121003C-8F78-4E59-879B-98B38701C7BF}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3A45DAF3-F395-4947-8D67-42B727933121}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3A45DAF3-F395-4947-8D67-42B727933121}"/>
   </bookViews>
   <sheets>
     <sheet name="발주서" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">발주서!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">발주서!$A$28:$K$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">발주서!$A$1:$K$27</definedName>
     <definedName name="동동">'[1](세대별)옵션'!$A$2:$A$5649</definedName>
     <definedName name="수">'[1](세대별)옵션'!$G$2:$G$5649</definedName>
     <definedName name="품품">'[1](세대별)옵션'!$E$2:$E$5649</definedName>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>자 재 발 주 의 뢰 서</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -65,15 +65,7 @@
     <t>납품장소</t>
   </si>
   <si>
-    <t>용인시 처인구 포곡읍 금어리646(2게이트)/도착전 미리 전화주세요.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>작 성 자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>서재형 과장</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -81,27 +73,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>김일홍 소장</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>010.5098.6888</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>현 장 명</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>용인금어지구 한라 에피트</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>납품일자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.07.29</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -145,58 +121,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>■ 경량골조(단위세대)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>STUD50형</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>L:2,600</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EA</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>STUD100형</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>L:2,700</t>
-  </si>
-  <si>
-    <t>EA</t>
-  </si>
-  <si>
-    <t>M/U세대</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>M/U세대</t>
-  </si>
-  <si>
-    <t>DL-STUD100형(문틀보강)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>RUNNER50형</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>L:3,000</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>RUNNER100형</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>L:3,000</t>
-  </si>
-  <si>
     <t xml:space="preserve">연락처: </t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -205,11 +129,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="yyyy\.mm\.dd"/>
-    <numFmt numFmtId="177" formatCode="&quot;*&quot;#&quot;회차&quot;"/>
     <numFmt numFmtId="178" formatCode="#,###"/>
     <numFmt numFmtId="179" formatCode="#,##0_);[Red]\(#,##0\);"/>
     <numFmt numFmtId="180" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -290,7 +213,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -317,18 +240,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -471,45 +388,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -638,18 +516,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -657,47 +526,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="176" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -708,46 +541,22 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
@@ -762,65 +571,116 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -80238,7 +80098,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.140625" customWidth="1"/>
@@ -80254,1217 +80114,586 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="4" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="6">
-        <v>45861</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="7" t="s">
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="47"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+    </row>
+    <row r="3" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-    </row>
-    <row r="3" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="B3" s="45"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="E3" s="47"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+    </row>
+    <row r="4" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="7" t="s">
+      <c r="B4" s="48"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="12" t="s">
+      <c r="E4" s="47"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-    </row>
-    <row r="4" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
     </row>
     <row r="5" spans="1:15" ht="10.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:15" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="41"/>
+      <c r="E6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19" t="s">
+      <c r="J6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="20" t="s">
+      <c r="K6" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="23" t="s">
-        <v>27</v>
+      <c r="A7" s="35"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="10">
+        <f t="shared" ref="I7" si="0">G7+H7</f>
+        <v>0</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="25">
-        <v>1</v>
+      <c r="J7" s="12" t="str">
+        <f t="shared" ref="J7" si="1">IFERROR(I7/F7,"-")</f>
+        <v>-</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="28"/>
+      <c r="K7" s="13"/>
     </row>
     <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="32"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="33">
-        <f t="shared" ref="I8:I22" si="0">G8+H8</f>
+      <c r="A8" s="35"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="10">
+        <f t="shared" ref="I8:I22" si="2">G8+H8</f>
         <v>0</v>
       </c>
-      <c r="J8" s="35" t="str">
-        <f t="shared" ref="J8:J27" si="1">IFERROR(I8/F8,"-")</f>
+      <c r="J8" s="12" t="str">
+        <f t="shared" ref="J8:J27" si="3">IFERROR(I8/F8,"-")</f>
         <v>-</v>
       </c>
-      <c r="K8" s="36"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="39"/>
+      <c r="K8" s="13"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="16"/>
     </row>
     <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="32"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="33">
-        <f t="shared" si="0"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J9" s="35" t="str">
-        <f t="shared" si="1"/>
+      <c r="J9" s="12" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="K9" s="36"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="40"/>
+      <c r="K9" s="13"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="17"/>
     </row>
     <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="29" t="s">
-        <v>28</v>
+      <c r="A10" s="35"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30" t="s">
-        <v>32</v>
+      <c r="J10" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
       </c>
-      <c r="D10" s="30"/>
-      <c r="E10" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="32">
-        <v>373</v>
-      </c>
-      <c r="G10" s="33"/>
-      <c r="H10" s="34">
-        <v>410</v>
-      </c>
-      <c r="I10" s="33">
-        <f t="shared" si="0"/>
-        <v>410</v>
-      </c>
-      <c r="J10" s="35">
-        <f t="shared" si="1"/>
-        <v>1.0991957104557641</v>
-      </c>
-      <c r="K10" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="N10" s="37"/>
-      <c r="O10" s="40"/>
+      <c r="K10" s="18"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="17"/>
     </row>
     <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="29" t="s">
-        <v>31</v>
+      <c r="A11" s="35"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30" t="s">
-        <v>32</v>
+      <c r="J11" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
       </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="32">
-        <v>157</v>
-      </c>
-      <c r="G11" s="33"/>
-      <c r="H11" s="34">
-        <v>200</v>
-      </c>
-      <c r="I11" s="33">
-        <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-      <c r="J11" s="35">
-        <f t="shared" si="1"/>
-        <v>1.2738853503184713</v>
-      </c>
-      <c r="K11" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="N11" s="37"/>
-      <c r="O11" s="40"/>
+      <c r="K11" s="18"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="17"/>
     </row>
     <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="29" t="s">
-        <v>36</v>
+      <c r="A12" s="35"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30" t="s">
-        <v>32</v>
+      <c r="J12" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
       </c>
-      <c r="D12" s="30"/>
-      <c r="E12" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="32">
-        <v>15</v>
-      </c>
-      <c r="G12" s="33"/>
-      <c r="H12" s="34">
-        <v>30</v>
-      </c>
-      <c r="I12" s="33">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="J12" s="35">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="K12" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="N12" s="37"/>
-      <c r="O12" s="40"/>
+      <c r="K12" s="18"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="17"/>
     </row>
     <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="29" t="s">
-        <v>37</v>
+      <c r="A13" s="35"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30" t="s">
-        <v>38</v>
+      <c r="J13" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
       </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="32">
-        <v>71</v>
-      </c>
-      <c r="G13" s="33"/>
-      <c r="H13" s="34">
-        <v>90</v>
-      </c>
-      <c r="I13" s="33">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-      <c r="J13" s="35">
-        <f t="shared" si="1"/>
-        <v>1.267605633802817</v>
-      </c>
-      <c r="K13" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="N13" s="37"/>
-      <c r="O13" s="40"/>
+      <c r="K13" s="18"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="17"/>
     </row>
     <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="29" t="s">
-        <v>39</v>
+      <c r="A14" s="35"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30" t="s">
-        <v>40</v>
+      <c r="J14" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
       </c>
-      <c r="D14" s="30"/>
-      <c r="E14" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="32">
-        <v>42</v>
-      </c>
-      <c r="G14" s="33"/>
-      <c r="H14" s="34">
-        <v>60</v>
-      </c>
-      <c r="I14" s="33">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="J14" s="35">
-        <f t="shared" si="1"/>
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="K14" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="N14" s="37"/>
-      <c r="O14" s="40"/>
+      <c r="K14" s="18"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="17"/>
     </row>
     <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="42"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="33">
-        <f t="shared" si="0"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J15" s="35" t="str">
-        <f t="shared" si="1"/>
+      <c r="J15" s="12" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="K15" s="44"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
+      <c r="K15" s="19"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
     </row>
     <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="29"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="33">
-        <f t="shared" si="0"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J16" s="35" t="str">
-        <f t="shared" si="1"/>
+      <c r="J16" s="12" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="K16" s="45"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="40"/>
+      <c r="K16" s="20"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="17"/>
     </row>
     <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="29"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="33">
-        <f t="shared" si="0"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J17" s="35" t="str">
-        <f t="shared" si="1"/>
+      <c r="J17" s="12" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="K17" s="41"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="40"/>
+      <c r="K17" s="18"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="17"/>
     </row>
     <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="29"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="33">
-        <f t="shared" si="0"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="35" t="str">
-        <f t="shared" si="1"/>
+      <c r="J18" s="12" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="K18" s="41"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="40"/>
+      <c r="K18" s="18"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="17"/>
     </row>
     <row r="19" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="29"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="33">
-        <f t="shared" si="0"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="35" t="str">
-        <f t="shared" si="1"/>
+      <c r="J19" s="12" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="K19" s="41"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="40"/>
+      <c r="K19" s="18"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="17"/>
     </row>
     <row r="20" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="29"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="33">
-        <f t="shared" si="0"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="35" t="str">
-        <f t="shared" si="1"/>
+      <c r="J20" s="12" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="K20" s="41"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="40"/>
+      <c r="K20" s="18"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="17"/>
     </row>
     <row r="21" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="29"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="33">
-        <f t="shared" si="0"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="35" t="str">
-        <f t="shared" si="1"/>
+      <c r="J21" s="12" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="K21" s="41"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="40"/>
+      <c r="K21" s="18"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="17"/>
     </row>
     <row r="22" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="42"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="33">
-        <f t="shared" si="0"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J22" s="35" t="str">
-        <f t="shared" si="1"/>
+      <c r="J22" s="12" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="K22" s="47"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="40"/>
+      <c r="K22" s="21"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
     </row>
     <row r="23" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="29"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="35" t="str">
-        <f t="shared" si="1"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="12" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="K23" s="50"/>
-      <c r="N23" s="37"/>
-      <c r="O23" s="40"/>
+      <c r="K23" s="24"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="17"/>
     </row>
     <row r="24" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="35" t="str">
-        <f t="shared" si="1"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="12" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="K24" s="50"/>
-      <c r="N24" s="37"/>
-      <c r="O24" s="40"/>
+      <c r="K24" s="24"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="17"/>
     </row>
     <row r="25" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="29"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="35" t="str">
-        <f t="shared" si="1"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="12" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="K25" s="50"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="40"/>
+      <c r="K25" s="24"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="17"/>
     </row>
     <row r="26" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="29"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="35" t="str">
-        <f t="shared" si="1"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="12" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="K26" s="50"/>
-      <c r="N26" s="37"/>
-      <c r="O26" s="40"/>
+      <c r="K26" s="24"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="17"/>
     </row>
     <row r="27" spans="1:15" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="51"/>
-      <c r="B27" s="52"/>
-      <c r="C27" s="53"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="58" t="str">
-        <f t="shared" si="1"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="29" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="K27" s="59"/>
-      <c r="N27" s="37"/>
-      <c r="O27" s="40"/>
-    </row>
-    <row r="28" spans="1:15" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-    </row>
-    <row r="30" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-    </row>
-    <row r="31" spans="1:15" ht="22.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-    </row>
-    <row r="32" spans="1:15" ht="10.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:15" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="I33" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="J33" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="K33" s="22" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="33">
-        <f t="shared" ref="I34" si="2">G34+H34</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="35" t="str">
-        <f t="shared" ref="J34" si="3">IFERROR(I34/F34,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="K34" s="36"/>
-    </row>
-    <row r="35" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="29"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="33">
-        <f t="shared" ref="I35:I49" si="4">G35+H35</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="35" t="str">
-        <f t="shared" ref="J35:J54" si="5">IFERROR(I35/F35,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="K35" s="36"/>
-      <c r="M35" s="37"/>
-      <c r="N35" s="38"/>
-      <c r="O35" s="39"/>
-    </row>
-    <row r="36" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="29"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J36" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K36" s="36"/>
-      <c r="N36" s="37"/>
-      <c r="O36" s="40"/>
-    </row>
-    <row r="37" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J37" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K37" s="41"/>
-      <c r="N37" s="37"/>
-      <c r="O37" s="40"/>
-    </row>
-    <row r="38" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="34"/>
-      <c r="I38" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J38" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K38" s="41"/>
-      <c r="N38" s="37"/>
-      <c r="O38" s="40"/>
-    </row>
-    <row r="39" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="33"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J39" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K39" s="41"/>
-      <c r="N39" s="37"/>
-      <c r="O39" s="40"/>
-    </row>
-    <row r="40" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="29"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J40" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K40" s="41"/>
-      <c r="N40" s="37"/>
-      <c r="O40" s="40"/>
-    </row>
-    <row r="41" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="29"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="34"/>
-      <c r="I41" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J41" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K41" s="41"/>
-      <c r="N41" s="37"/>
-      <c r="O41" s="40"/>
-    </row>
-    <row r="42" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="42"/>
-      <c r="B42" s="43"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K42" s="44"/>
-      <c r="N42" s="40"/>
-      <c r="O42" s="40"/>
-    </row>
-    <row r="43" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J43" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K43" s="45"/>
-      <c r="N43" s="37"/>
-      <c r="O43" s="40"/>
-    </row>
-    <row r="44" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="29"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="34"/>
-      <c r="I44" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J44" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K44" s="41"/>
-      <c r="N44" s="37"/>
-      <c r="O44" s="40"/>
-    </row>
-    <row r="45" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="29"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="33"/>
-      <c r="H45" s="34"/>
-      <c r="I45" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J45" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K45" s="41"/>
-      <c r="N45" s="37"/>
-      <c r="O45" s="40"/>
-    </row>
-    <row r="46" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="29"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="33"/>
-      <c r="H46" s="34"/>
-      <c r="I46" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J46" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K46" s="41"/>
-      <c r="N46" s="37"/>
-      <c r="O46" s="40"/>
-    </row>
-    <row r="47" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="29"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="33"/>
-      <c r="H47" s="34"/>
-      <c r="I47" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J47" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K47" s="41"/>
-      <c r="N47" s="37"/>
-      <c r="O47" s="40"/>
-    </row>
-    <row r="48" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="29"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="33"/>
-      <c r="H48" s="34"/>
-      <c r="I48" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J48" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K48" s="41"/>
-      <c r="N48" s="37"/>
-      <c r="O48" s="40"/>
-    </row>
-    <row r="49" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="42"/>
-      <c r="B49" s="43"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="33"/>
-      <c r="H49" s="34"/>
-      <c r="I49" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J49" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K49" s="47"/>
-      <c r="N49" s="40"/>
-      <c r="O49" s="40"/>
-    </row>
-    <row r="50" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="29"/>
-      <c r="B50" s="30"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="49"/>
-      <c r="I50" s="48"/>
-      <c r="J50" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K50" s="50"/>
-      <c r="N50" s="37"/>
-      <c r="O50" s="40"/>
-    </row>
-    <row r="51" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="29"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="49"/>
-      <c r="I51" s="48"/>
-      <c r="J51" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K51" s="50"/>
-      <c r="N51" s="37"/>
-      <c r="O51" s="40"/>
-    </row>
-    <row r="52" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="29"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="49"/>
-      <c r="I52" s="48"/>
-      <c r="J52" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K52" s="50"/>
-      <c r="N52" s="37"/>
-      <c r="O52" s="40"/>
-    </row>
-    <row r="53" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="29"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="49"/>
-      <c r="I53" s="48"/>
-      <c r="J53" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K53" s="50"/>
-      <c r="N53" s="37"/>
-      <c r="O53" s="40"/>
-    </row>
-    <row r="54" spans="1:15" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="51"/>
-      <c r="B54" s="52"/>
-      <c r="C54" s="53"/>
-      <c r="D54" s="52"/>
-      <c r="E54" s="54"/>
-      <c r="F54" s="55"/>
-      <c r="G54" s="56"/>
-      <c r="H54" s="57"/>
-      <c r="I54" s="56"/>
-      <c r="J54" s="58" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-      <c r="K54" s="59"/>
-      <c r="N54" s="37"/>
-      <c r="O54" s="40"/>
+      <c r="K27" s="30"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="112">
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="H29:H31"/>
-    <mergeCell ref="I29:I31"/>
-    <mergeCell ref="J29:J31"/>
-    <mergeCell ref="K29:K31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
+  <mergeCells count="56">
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A25:B25"/>
@@ -81477,48 +80706,6 @@
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.43307086614173229" right="0.43307086614173229" top="0.55118110236220474" bottom="0.55118110236220474" header="0.11811023622047245" footer="0.11811023622047245"/>
